--- a/checkrates/week-20/Analisis_Checkrates_7d.xlsx
+++ b/checkrates/week-20/Analisis_Checkrates_7d.xlsx
@@ -569,7 +569,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W20 · 12-18 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W20 · 12-18 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W20 · 12-18 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W20 · 12-18 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -1338,7 +1338,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W20 · 12-18 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -1892,7 +1892,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W20 · 12-18 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -5099,7 +5099,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W20 · 12-18 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -9398,7 +9398,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W20 · 12-18 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -10736,7 +10736,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W20 · 12-18 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -14330,7 +14330,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W20 · 12-18 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -14669,7 +14669,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W20 · 12-18 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -18752,7 +18752,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W20 · 12-18 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -18905,7 +18905,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W20 · 12-18 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -19058,7 +19058,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W20 · 12-18 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -19218,7 +19218,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W20 · 12-18 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -23822,7 +23822,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W20 · 12-18 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -28121,7 +28121,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W20 · 12-18 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -32420,7 +32420,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W20 · 12-18 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -34278,7 +34278,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W20 · 12-18 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -37872,7 +37872,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W20 · 12-18 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -38291,7 +38291,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W20 · 12-18 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -42584,7 +42584,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W20 · 12-18 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -42744,7 +42744,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W20 · 12-18 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -47342,7 +47342,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W20 · 12-18 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -47502,7 +47502,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W20 · 12-18 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -50981,7 +50981,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W20 · 12-18 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -55280,7 +55280,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W20 · 12-18 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -59579,7 +59579,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W20 · 12-18 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -61357,7 +61357,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W20 · 12-18 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -64951,7 +64951,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W20 · 12-18 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -65370,7 +65370,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W20 · 12-18 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -69669,7 +69669,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W20 · 12-18 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -73967,7 +73967,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W20 · 12-18 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -77961,7 +77961,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W20 · 12-18 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -80139,7 +80139,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W20 · 12-18 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -83733,7 +83733,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W20 · 12-18 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -84152,7 +84152,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W20 · 12-18 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-20/Analisis_Checkrates_7d.xlsx
+++ b/checkrates/week-20/Analisis_Checkrates_7d.xlsx
@@ -569,7 +569,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
+          <t>Generado: 23/05/2026 02:24 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
+          <t>Generado: 23/05/2026 02:24 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
+          <t>Generado: 23/05/2026 02:24 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
+          <t>Generado: 23/05/2026 02:24 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -1338,7 +1338,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
+          <t>Generado: 23/05/2026 02:24 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -1892,7 +1892,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
+          <t>Generado: 23/05/2026 02:24 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -5099,7 +5099,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
+          <t>Generado: 23/05/2026 02:24 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -9398,7 +9398,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
+          <t>Generado: 23/05/2026 02:24 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -10736,7 +10736,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
+          <t>Generado: 23/05/2026 02:24 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -14330,7 +14330,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
+          <t>Generado: 23/05/2026 02:24 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -14669,7 +14669,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
+          <t>Generado: 23/05/2026 02:24 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -18752,7 +18752,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
+          <t>Generado: 23/05/2026 02:24 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -18905,7 +18905,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
+          <t>Generado: 23/05/2026 02:24 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -19058,7 +19058,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
+          <t>Generado: 23/05/2026 02:24 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -19218,7 +19218,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
+          <t>Generado: 23/05/2026 02:24 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -23822,7 +23822,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
+          <t>Generado: 23/05/2026 02:24 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -28121,7 +28121,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
+          <t>Generado: 23/05/2026 02:24 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -32420,7 +32420,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
+          <t>Generado: 23/05/2026 02:24 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -34278,7 +34278,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
+          <t>Generado: 23/05/2026 02:24 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -37872,7 +37872,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
+          <t>Generado: 23/05/2026 02:24 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -38291,7 +38291,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
+          <t>Generado: 23/05/2026 02:24 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -42584,7 +42584,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
+          <t>Generado: 23/05/2026 02:24 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -42744,7 +42744,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
+          <t>Generado: 23/05/2026 02:24 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -47342,7 +47342,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
+          <t>Generado: 23/05/2026 02:24 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -47502,7 +47502,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
+          <t>Generado: 23/05/2026 02:24 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -50981,7 +50981,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
+          <t>Generado: 23/05/2026 02:24 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -55280,7 +55280,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
+          <t>Generado: 23/05/2026 02:24 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -59579,7 +59579,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
+          <t>Generado: 23/05/2026 02:24 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -61357,7 +61357,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
+          <t>Generado: 23/05/2026 02:24 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -64951,7 +64951,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
+          <t>Generado: 23/05/2026 02:24 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -65370,7 +65370,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
+          <t>Generado: 23/05/2026 02:24 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -69669,7 +69669,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
+          <t>Generado: 23/05/2026 02:24 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -73967,7 +73967,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
+          <t>Generado: 23/05/2026 02:24 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -77961,7 +77961,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
+          <t>Generado: 23/05/2026 02:24 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -80139,7 +80139,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
+          <t>Generado: 23/05/2026 02:24 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -83733,7 +83733,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
+          <t>Generado: 23/05/2026 02:24 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -84152,7 +84152,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
+          <t>Generado: 23/05/2026 02:24 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-20/Analisis_Checkrates_7d.xlsx
+++ b/checkrates/week-20/Analisis_Checkrates_7d.xlsx
@@ -569,7 +569,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 02:24 · W20 · 12-18 may 2026</t>
+          <t>Generado: 23/05/2026 22:34 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 02:24 · W20 · 12-18 may 2026</t>
+          <t>Generado: 23/05/2026 22:34 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 02:24 · W20 · 12-18 may 2026</t>
+          <t>Generado: 23/05/2026 22:34 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 02:24 · W20 · 12-18 may 2026</t>
+          <t>Generado: 23/05/2026 22:34 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -1338,7 +1338,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 02:24 · W20 · 12-18 may 2026</t>
+          <t>Generado: 23/05/2026 22:34 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -1892,7 +1892,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 02:24 · W20 · 12-18 may 2026</t>
+          <t>Generado: 23/05/2026 22:34 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -5099,7 +5099,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 02:24 · W20 · 12-18 may 2026</t>
+          <t>Generado: 23/05/2026 22:34 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -9398,7 +9398,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 02:24 · W20 · 12-18 may 2026</t>
+          <t>Generado: 23/05/2026 22:34 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -10736,7 +10736,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 02:24 · W20 · 12-18 may 2026</t>
+          <t>Generado: 23/05/2026 22:34 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -14330,7 +14330,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 02:24 · W20 · 12-18 may 2026</t>
+          <t>Generado: 23/05/2026 22:34 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -14669,7 +14669,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 02:24 · W20 · 12-18 may 2026</t>
+          <t>Generado: 23/05/2026 22:34 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -18752,7 +18752,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 02:24 · W20 · 12-18 may 2026</t>
+          <t>Generado: 23/05/2026 22:34 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -18905,7 +18905,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 02:24 · W20 · 12-18 may 2026</t>
+          <t>Generado: 23/05/2026 22:34 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -19058,7 +19058,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 02:24 · W20 · 12-18 may 2026</t>
+          <t>Generado: 23/05/2026 22:34 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -19218,7 +19218,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 02:24 · W20 · 12-18 may 2026</t>
+          <t>Generado: 23/05/2026 22:34 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -23822,7 +23822,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 02:24 · W20 · 12-18 may 2026</t>
+          <t>Generado: 23/05/2026 22:34 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -28121,7 +28121,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 02:24 · W20 · 12-18 may 2026</t>
+          <t>Generado: 23/05/2026 22:34 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -32420,7 +32420,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 02:24 · W20 · 12-18 may 2026</t>
+          <t>Generado: 23/05/2026 22:34 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -34278,7 +34278,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 02:24 · W20 · 12-18 may 2026</t>
+          <t>Generado: 23/05/2026 22:34 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -37872,7 +37872,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 02:24 · W20 · 12-18 may 2026</t>
+          <t>Generado: 23/05/2026 22:34 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -38291,7 +38291,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 02:24 · W20 · 12-18 may 2026</t>
+          <t>Generado: 23/05/2026 22:34 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -42584,7 +42584,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 02:24 · W20 · 12-18 may 2026</t>
+          <t>Generado: 23/05/2026 22:34 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -42744,7 +42744,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 02:24 · W20 · 12-18 may 2026</t>
+          <t>Generado: 23/05/2026 22:34 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -47342,7 +47342,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 02:24 · W20 · 12-18 may 2026</t>
+          <t>Generado: 23/05/2026 22:34 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -47502,7 +47502,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 02:24 · W20 · 12-18 may 2026</t>
+          <t>Generado: 23/05/2026 22:34 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -50981,7 +50981,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 02:24 · W20 · 12-18 may 2026</t>
+          <t>Generado: 23/05/2026 22:34 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -55280,7 +55280,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 02:24 · W20 · 12-18 may 2026</t>
+          <t>Generado: 23/05/2026 22:34 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -59579,7 +59579,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 02:24 · W20 · 12-18 may 2026</t>
+          <t>Generado: 23/05/2026 22:34 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -61357,7 +61357,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 02:24 · W20 · 12-18 may 2026</t>
+          <t>Generado: 23/05/2026 22:34 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -64951,7 +64951,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 02:24 · W20 · 12-18 may 2026</t>
+          <t>Generado: 23/05/2026 22:34 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -65370,7 +65370,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 02:24 · W20 · 12-18 may 2026</t>
+          <t>Generado: 23/05/2026 22:34 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -69669,7 +69669,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 02:24 · W20 · 12-18 may 2026</t>
+          <t>Generado: 23/05/2026 22:34 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -73967,7 +73967,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 02:24 · W20 · 12-18 may 2026</t>
+          <t>Generado: 23/05/2026 22:34 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -77961,7 +77961,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 02:24 · W20 · 12-18 may 2026</t>
+          <t>Generado: 23/05/2026 22:34 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -80139,7 +80139,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 02:24 · W20 · 12-18 may 2026</t>
+          <t>Generado: 23/05/2026 22:34 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -83733,7 +83733,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 02:24 · W20 · 12-18 may 2026</t>
+          <t>Generado: 23/05/2026 22:34 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -84152,7 +84152,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 02:24 · W20 · 12-18 may 2026</t>
+          <t>Generado: 23/05/2026 22:34 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-20/Analisis_Checkrates_7d.xlsx
+++ b/checkrates/week-20/Analisis_Checkrates_7d.xlsx
@@ -569,7 +569,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 22:34 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 03:40 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 22:34 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 03:40 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 22:34 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 03:40 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 22:34 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 03:40 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -1338,7 +1338,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 22:34 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 03:40 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -1892,7 +1892,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 22:34 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 03:40 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -5099,7 +5099,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 22:34 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 03:40 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -9398,7 +9398,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 22:34 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 03:40 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -10736,7 +10736,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 22:34 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 03:40 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -14330,7 +14330,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 22:34 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 03:40 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -14669,7 +14669,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 22:34 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 03:40 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -18752,7 +18752,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 22:34 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 03:40 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -18905,7 +18905,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 22:34 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 03:40 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -19058,7 +19058,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 22:34 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 03:40 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -19218,7 +19218,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 22:34 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 03:40 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -23822,7 +23822,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 22:34 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 03:40 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -28121,7 +28121,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 22:34 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 03:40 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -32420,7 +32420,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 22:34 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 03:40 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -34278,7 +34278,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 22:34 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 03:40 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -37872,7 +37872,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 22:34 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 03:40 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -38291,7 +38291,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 22:34 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 03:40 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -42584,7 +42584,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 22:34 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 03:40 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -42744,7 +42744,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 22:34 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 03:40 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -47342,7 +47342,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 22:34 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 03:40 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -47502,7 +47502,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 22:34 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 03:40 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -50981,7 +50981,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 22:34 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 03:40 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -55280,7 +55280,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 22:34 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 03:40 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -59579,7 +59579,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 22:34 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 03:40 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -61357,7 +61357,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 22:34 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 03:40 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -64951,7 +64951,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 22:34 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 03:40 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -65370,7 +65370,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 22:34 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 03:40 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -69669,7 +69669,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 22:34 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 03:40 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -73967,7 +73967,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 22:34 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 03:40 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -77961,7 +77961,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 22:34 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 03:40 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -80139,7 +80139,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 22:34 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 03:40 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -83733,7 +83733,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 22:34 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 03:40 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -84152,7 +84152,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 22:34 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 03:40 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-20/Analisis_Checkrates_7d.xlsx
+++ b/checkrates/week-20/Analisis_Checkrates_7d.xlsx
@@ -569,7 +569,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 03:40 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 03:40 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 03:40 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 03:40 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -1338,7 +1338,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 03:40 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -1892,7 +1892,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 03:40 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -5099,7 +5099,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 03:40 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -9398,7 +9398,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 03:40 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -10736,7 +10736,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 03:40 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -14330,7 +14330,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 03:40 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -14669,7 +14669,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 03:40 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -18752,7 +18752,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 03:40 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -18905,7 +18905,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 03:40 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -19058,7 +19058,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 03:40 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -19218,7 +19218,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 03:40 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -23822,7 +23822,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 03:40 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -28121,7 +28121,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 03:40 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -32420,7 +32420,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 03:40 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -34278,7 +34278,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 03:40 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -37872,7 +37872,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 03:40 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -38291,7 +38291,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 03:40 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -42584,7 +42584,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 03:40 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -42744,7 +42744,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 03:40 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -47342,7 +47342,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 03:40 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -47502,7 +47502,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 03:40 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -50981,7 +50981,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 03:40 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -55280,7 +55280,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 03:40 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -59579,7 +59579,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 03:40 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -61357,7 +61357,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 03:40 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -64951,7 +64951,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 03:40 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -65370,7 +65370,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 03:40 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -69669,7 +69669,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 03:40 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -73967,7 +73967,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 03:40 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -77961,7 +77961,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 03:40 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -80139,7 +80139,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 03:40 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -83733,7 +83733,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 03:40 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -84152,7 +84152,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 03:40 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-20/Analisis_Checkrates_7d.xlsx
+++ b/checkrates/week-20/Analisis_Checkrates_7d.xlsx
@@ -569,7 +569,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -1338,7 +1338,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -1892,7 +1892,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -5099,7 +5099,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -9398,7 +9398,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -10736,7 +10736,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -14330,7 +14330,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -14669,7 +14669,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -18752,7 +18752,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -18905,7 +18905,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -19058,7 +19058,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -19218,7 +19218,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -23822,7 +23822,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -28121,7 +28121,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -32420,7 +32420,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -34278,7 +34278,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -37872,7 +37872,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -38291,7 +38291,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -42584,7 +42584,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -42744,7 +42744,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -47342,7 +47342,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -47502,7 +47502,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -50981,7 +50981,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -55280,7 +55280,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -59579,7 +59579,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -61357,7 +61357,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -64951,7 +64951,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -65370,7 +65370,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -69669,7 +69669,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -73967,7 +73967,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -77961,7 +77961,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -80139,7 +80139,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -83733,7 +83733,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -84152,7 +84152,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
